--- a/public/sample.xlsx
+++ b/public/sample.xlsx
@@ -1039,7 +1039,8 @@
   <dimension ref="A1:AO9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
     <col min="10" max="10" width="25.375" customWidth="1"/>
     <col min="22" max="22" width="10.375" customWidth="1"/>
     <col min="29" max="29" width="13.375" customWidth="1"/>
